--- a/daily_matches/job_matches_2026-06-22.xlsx
+++ b/daily_matches/job_matches_2026-06-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Openshift)</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BDO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.3</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python</t>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, S3, Glue, Athena, Redshift</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,102 +496,102 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e45a515134d07c83</t>
+          <t>https://www.indeed.com/viewjob?jk=2fe3e1ce3f976c6b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>^AI ML Engineer - 6352112</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, LLaMA, Mistral, Prompt Engineering, Azure ML, Azure ML Studio, Snowflake</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, S3, EC2, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ec416265b4c0a69</t>
+          <t>https://www.indeed.com/viewjob?jk=e938eb8fe4edc00e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>^AI ML Engineer - 6352113</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, LLaMA, Mistral, Prompt Engineering, Azure ML, Azure ML Studio, Snowflake</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, S3, EC2, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f83495d36217ec1</t>
+          <t>https://www.indeed.com/viewjob?jk=ec9b4a262952d700</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Developer Experience</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Seurat Technologies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, S3, Redshift, BigQuery, Data Lake, Kinesis, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de0223923f1ebfa4</t>
+          <t>https://www.indeed.com/viewjob?jk=e1efe0d50d8101c2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Infrastructure/Backend Engineer</t>
+          <t>Python Backend Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mLabs</t>
+          <t>ClinDCast LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, R, Scala, Optimization</t>
+          <t>LangChain, LLaMA, Pinecone, FastAPI, Docker, PostgreSQL, MongoDB, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4dbeea3f653f295</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ccacef123a31f7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>AI Data Scientist (Transcriptomics &amp; cfRNA for Alzheimer’s Disease Research)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>Superfluid DX, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, XGBoost, EC2, AKS, CI/CD, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,42 +671,322 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=723554d227144372</t>
+          <t>https://www.indeed.com/viewjob?jk=28c54b52a343be8c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jr Data Scientist</t>
+          <t>Senior Specialist - Data Sciences</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Pinecone, Docker, Kubernetes, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=507100aa20b0b5d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ad7de4231b3a43e</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Software Development Engineer III</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Palmetto Clean Technology</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, Git, Kafka, MongoDB, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8062e3d6b372dc03</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Data Mining</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Motional</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, AKS, CI/CD, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df4a0d86df699f9d</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Data Mining</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Motional</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, AKS, CI/CD, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39367ce9efa70316</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Engineer II - AI Foundations</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Best Buy</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, PyTorch, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f7906f631ba9c0ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sr. Marketing Data Analyst</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>WebstaurantStore</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Lititz, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Data Lake, BigQuery, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3913ab1223723ad1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Associate - Data Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Nomura</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Lake, Dataflow, CI/CD, Jenkins, Git, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d897690a96d924bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Identity and Access Management Consultant</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>Atlanta, GA, US USA</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D16" t="n">
         <v>10</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, Git, Databricks, PySpark, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8559a29405401b33</t>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5715a70a830bab49</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-22.xlsx
+++ b/daily_matches/job_matches_2026-06-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>AI/ML Engineer - Supply Chain</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BDO</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.8</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, S3, Glue, Athena, Redshift</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, MLflow, FastAPI, Docker, Kubernetes, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fe3e1ce3f976c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=c337227860ec1abc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>Agentic AI Engineer II - Cyber Analytics</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, S3, EC2, Docker</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e938eb8fe4edc00e</t>
+          <t>https://www.indeed.com/viewjob?jk=705011c4830be681</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Skillable</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, S3, EC2, Docker</t>
+          <t>Generative AI, RAG, Redshift, BigQuery, Synapse, Data Lake, CI/CD, Snowflake, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec9b4a262952d700</t>
+          <t>https://www.indeed.com/viewjob?jk=311fae6e7852845c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Systems Integration Engineer 3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Seurat Technologies</t>
+          <t>UC San Diego</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, BigQuery, Data Lake, Kinesis, Snowflake, Databricks, BigQuery, Redshift</t>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1efe0d50d8101c2</t>
+          <t>https://www.indeed.com/viewjob?jk=656b4089fd66ca54</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Python Backend Engineer</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ClinDCast LLC</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, LLaMA, Pinecone, FastAPI, Docker, PostgreSQL, MongoDB, NoSQL, Python, SQL</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, Pinecone, MLflow, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ccacef123a31f7</t>
+          <t>https://www.indeed.com/viewjob?jk=679b995b3aa9e079</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Data Scientist (Transcriptomics &amp; cfRNA for Alzheimer’s Disease Research)</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Superfluid DX, Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, XGBoost, EC2, AKS, CI/CD, Git</t>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28c54b52a343be8c</t>
+          <t>https://www.indeed.com/viewjob?jk=8e317b647d670c88</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Sciences</t>
+          <t>Full Stack Software Engineer III - Supply Chain and Operations</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Pinecone, Docker, Kubernetes, Python, SQL</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507100aa20b0b5d5</t>
+          <t>https://www.indeed.com/viewjob?jk=74c5b0db361ef939</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CSC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, MySQL, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad7de4231b3a43e</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0b512dd7f151fe</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Palmetto Clean Technology</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, Git, Kafka, MongoDB, NoSQL, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8062e3d6b372dc03</t>
+          <t>https://www.indeed.com/viewjob?jk=1105ec475da982ae</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Data Mining</t>
+          <t>Senior Performance Database Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Motional</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, AKS, CI/CD, Python, SQL, R, Scala</t>
+          <t>RAG, Redshift, CI/CD, Terraform, Redshift, PostgreSQL, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df4a0d86df699f9d</t>
+          <t>https://www.indeed.com/viewjob?jk=e4925c6e7012876a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Data Mining</t>
+          <t>AI/ML Engineer Intern</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Motional</t>
+          <t>T. Mims Corp.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, AKS, CI/CD, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, PyTorch, Git, PySpark, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39367ce9efa70316</t>
+          <t>https://www.indeed.com/viewjob?jk=21f2c5c9d37cc3c8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Engineer II - AI Foundations</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Best Buy</t>
+          <t>Cloudflare</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, BigQuery, Data Lake, BigQuery, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7906f631ba9c0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=0ee94685b3225387</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Marketing Data Analyst</t>
+          <t>UX Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WebstaurantStore</t>
+          <t>Charles River Analytics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lititz, PA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Data Lake, BigQuery, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>S3, EC2, Docker, Kubernetes, Git, MySQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3913ab1223723ad1</t>
+          <t>https://www.indeed.com/viewjob?jk=8c9d974e64a10e28</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>AI/ ML Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Crate and Barrel</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Lake, Dataflow, CI/CD, Jenkins, Git, Snowflake, Python, SQL, R</t>
+          <t>Machine Learning Engineer, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,42 +951,917 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d897690a96d924bc</t>
+          <t>https://www.indeed.com/viewjob?jk=dee23766e89bd264</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Identity and Access Management Consultant</t>
+          <t>AI / Machine Learning Talent</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>Ensemble Health Partners</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08104bdcbe65b056</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f828444f8849636</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Southern New Hampshire University</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Copilot, CI/CD, Git, PostgreSQL, MySQL, NoSQL, Python</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12abd2998788b1bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kharon</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>S3, EC2, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da47488f49b8866f</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Cybersecurity Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, FastAPI, Docker, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d37a189ba4e6054</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Platform Engineer II</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Acima Leasing</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5562bfd4f998c118</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, Kinesis, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Python</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da7ab691a0b00d67</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Python Engineer / Pipeline Developer (Local / Project-Based)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Brookfield, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, LLaMA, Copilot, Prompt Engineering, S3, Git, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=669ac7c33ef161fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Software Engineer L3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, Kubernetes, Terraform, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e673ea94a62ca6a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI &amp; Data Analytics Developer - Must be government clearance eligible</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Navaide</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, Git, Databricks, PySpark, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0225e45e2a1d63e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Raptive</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Keras, BigQuery, Snowflake, BigQuery, Python</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d72d6e1791e7297</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Interra Health</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Apache Airflow, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1318e82a9a194375</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Foster City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Generative AI, Jenkins, Git, MySQL, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d7edf6138a55eb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Software Quality Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc2bf61967411e59</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Scientist - R&amp;D (AI/ML)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Vermeer Corporation</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ames, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, MLflow, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2fbc91c8b1f3874b</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NextPower</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Folsom, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, Git, Snowflake, Databricks, PySpark, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e01d6adbf34f908b</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Privileged Access Management - Conjur Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nomura</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12fbf93f480098d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AI Engineer - Cloud Infrastructure</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Traversal</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>10</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5715a70a830bab49</t>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Pinecone, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2942edfcee98a38c</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>System Architect – Platform Engineering</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Kafka, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f81a3257ca39d82e</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Braze</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ecf6407a53ab4b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>KUNGFU.AI</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Terraform, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=197c3f9ed7f05177</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Software Engineer (Python)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Generative AI, S3, EC2, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=876694d10ba8f597</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Software Engineer (Python)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Generative AI, S3, EC2, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a1c95fea920c7ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer I - Java - Ace Studio Platform</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Sunrise, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, Jenkins, Git, Kafka, Cassandra, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61154a8efcdc6de3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Forward Deployment Engineer - Frontier AI Deployments</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Accellor</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8ed13132fb0a3b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Forward Deployment Engineer - Frontier AI Deployments</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Accellor</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a812c0236d393aa</t>
         </is>
       </c>
     </row>
